--- a/tests/fixtures/excel_basic/config/app.xlsx
+++ b/tests/fixtures/excel_basic/config/app.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
-    <sheet name="notes" sheetId="2" r:id="rId2"/>
+    <sheet name="_notes" sheetId="2" r:id="rId2"/>
     <sheet name="#draft" sheetId="3" r:id="rId3"/>
     <sheet name="secret" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
